--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O313"/>
+  <dimension ref="A1:O314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15161,6 +15161,53 @@
         <v>21.02</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B314" t="n">
+        <v>-647.63</v>
+      </c>
+      <c r="C314" t="n">
+        <v>156.72</v>
+      </c>
+      <c r="D314" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="F314" t="n">
+        <v>3.88000000000001</v>
+      </c>
+      <c r="G314" t="n">
+        <v>-462.75</v>
+      </c>
+      <c r="H314" t="n">
+        <v>-458.87</v>
+      </c>
+      <c r="I314" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="J314" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L314" t="n">
+        <v>-129.67</v>
+      </c>
+      <c r="M314" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="N314" t="n">
+        <v>133.88</v>
+      </c>
+      <c r="O314" t="n">
+        <v>-29.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O314"/>
+  <dimension ref="A1:O315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15220,6 +15220,53 @@
         <v>-29.36</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B315" t="n">
+        <v>277.67</v>
+      </c>
+      <c r="C315" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="D315" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="F315" t="n">
+        <v>-29.25</v>
+      </c>
+      <c r="G315" t="n">
+        <v>461.3700000000001</v>
+      </c>
+      <c r="H315" t="n">
+        <v>432.1200000000001</v>
+      </c>
+      <c r="I315" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="J315" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="n">
+        <v>-52.28</v>
+      </c>
+      <c r="M315" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N315" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="O315" t="n">
+        <v>-2.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,88 +417,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O315"/>
+  <dimension ref="A1:O316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15265,6 +15253,53 @@
       </c>
       <c r="O315" t="n">
         <v>-2.37</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B316" t="n">
+        <v>-109.83</v>
+      </c>
+      <c r="C316" t="n">
+        <v>-116.9</v>
+      </c>
+      <c r="D316" t="n">
+        <v>-272.08</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-331.69</v>
+      </c>
+      <c r="F316" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="G316" t="n">
+        <v>-830.5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-588.1</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J316" t="n">
+        <v>-272.69</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="n">
+        <v>-168.69</v>
+      </c>
+      <c r="M316" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N316" t="n">
+        <v>403.28</v>
+      </c>
+      <c r="O316" t="n">
+        <v>8.390000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15256,7 +15268,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15268,7 +15256,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O316"/>
+  <dimension ref="A1:O317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15302,6 +15302,53 @@
         <v>8.390000000000001</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B317" t="n">
+        <v>358.63</v>
+      </c>
+      <c r="C317" t="n">
+        <v>-409.93</v>
+      </c>
+      <c r="D317" t="n">
+        <v>267.26</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-434.35</v>
+      </c>
+      <c r="F317" t="n">
+        <v>-26.59999999999998</v>
+      </c>
+      <c r="G317" t="n">
+        <v>-218.39</v>
+      </c>
+      <c r="H317" t="n">
+        <v>-244.99</v>
+      </c>
+      <c r="I317" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="J317" t="n">
+        <v>268.67</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
+        <v>-196.62</v>
+      </c>
+      <c r="M317" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="N317" t="n">
+        <v>137.99</v>
+      </c>
+      <c r="O317" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15256,7 +15268,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15303,7 +15315,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15268,7 +15256,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15315,7 +15303,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,88 +417,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O317"/>
+  <dimension ref="A1:O318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15268,14 +15256,14 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
         <v>-109.83</v>
       </c>
       <c r="C316" t="n">
-        <v>-116.9</v>
+        <v>-113.62</v>
       </c>
       <c r="D316" t="n">
         <v>-272.08</v>
@@ -15287,10 +15275,10 @@
         <v>242.4</v>
       </c>
       <c r="G316" t="n">
-        <v>-830.5</v>
+        <v>-827.22</v>
       </c>
       <c r="H316" t="n">
-        <v>-588.1</v>
+        <v>-584.8200000000001</v>
       </c>
       <c r="I316" t="n">
         <v>0.61</v>
@@ -15315,7 +15303,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">
@@ -15359,6 +15347,53 @@
       </c>
       <c r="O317" t="n">
         <v>7.42</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B318" t="n">
+        <v>-189.9</v>
+      </c>
+      <c r="C318" t="n">
+        <v>-484.73</v>
+      </c>
+      <c r="D318" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="E318" t="n">
+        <v>-60</v>
+      </c>
+      <c r="F318" t="n">
+        <v>826.13</v>
+      </c>
+      <c r="G318" t="n">
+        <v>-749.33</v>
+      </c>
+      <c r="H318" t="n">
+        <v>76.79999999999995</v>
+      </c>
+      <c r="I318" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="J318" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="n">
+        <v>928.54</v>
+      </c>
+      <c r="M318" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="N318" t="n">
+        <v>-143.25</v>
+      </c>
+      <c r="O318" t="n">
+        <v>-6.62</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O318"/>
+  <dimension ref="A1:O319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15396,6 +15396,53 @@
         <v>-6.62</v>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B319" t="n">
+        <v>-248.2</v>
+      </c>
+      <c r="C319" t="n">
+        <v>451.12</v>
+      </c>
+      <c r="D319" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E319" t="n">
+        <v>-479.71</v>
+      </c>
+      <c r="F319" t="n">
+        <v>-588.35</v>
+      </c>
+      <c r="G319" t="n">
+        <v>-217.96</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-806.3099999999999</v>
+      </c>
+      <c r="I319" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="J319" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
+        <v>-741.03</v>
+      </c>
+      <c r="M319" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="N319" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="O319" t="n">
+        <v>12.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15256,7 +15268,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15303,7 +15315,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">
@@ -15350,7 +15362,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>46297</v>
       </c>
       <c r="B318" t="n">
@@ -15397,7 +15409,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>46304</v>
       </c>
       <c r="B319" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15268,7 +15256,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15315,7 +15303,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">
@@ -15362,7 +15350,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B318" t="n">
@@ -15409,7 +15397,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="B319" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O319"/>
+  <dimension ref="A1:O320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,7 +799,7 @@
         <v>-118.58</v>
       </c>
       <c r="G8" t="n">
-        <v>9.739999999999997</v>
+        <v>9.739999999999998</v>
       </c>
       <c r="H8" t="n">
         <v>-108.84</v>
@@ -1081,7 +1081,7 @@
         <v>2025.54</v>
       </c>
       <c r="G14" t="n">
-        <v>60.98999999999999</v>
+        <v>60.99</v>
       </c>
       <c r="H14" t="n">
         <v>2086.53</v>
@@ -2397,10 +2397,10 @@
         <v>32.43</v>
       </c>
       <c r="G42" t="n">
-        <v>-24.98</v>
+        <v>-24.97999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>7.450000000000003</v>
+        <v>7.45000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>-153.41</v>
@@ -2773,7 +2773,7 @@
         <v>-277.45</v>
       </c>
       <c r="G50" t="n">
-        <v>74.77</v>
+        <v>74.77000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>-202.68</v>
@@ -3149,7 +3149,7 @@
         <v>-793.46</v>
       </c>
       <c r="G58" t="n">
-        <v>-76.14000000000001</v>
+        <v>-76.14</v>
       </c>
       <c r="H58" t="n">
         <v>-869.6</v>
@@ -3572,7 +3572,7 @@
         <v>-377.48</v>
       </c>
       <c r="G67" t="n">
-        <v>1.670000000000023</v>
+        <v>1.670000000000016</v>
       </c>
       <c r="H67" t="n">
         <v>-375.81</v>
@@ -3622,7 +3622,7 @@
         <v>-332.61</v>
       </c>
       <c r="H68" t="n">
-        <v>-483.2099999999999</v>
+        <v>-483.21</v>
       </c>
       <c r="I68" t="n">
         <v>-168</v>
@@ -3995,7 +3995,7 @@
         <v>-198.55</v>
       </c>
       <c r="G76" t="n">
-        <v>1.54</v>
+        <v>1.539999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>-197.01</v>
@@ -4750,7 +4750,7 @@
         <v>288.92</v>
       </c>
       <c r="H92" t="n">
-        <v>50</v>
+        <v>49.99999999999994</v>
       </c>
       <c r="I92" t="n">
         <v>0.31</v>
@@ -5358,7 +5358,7 @@
         <v>-117.01</v>
       </c>
       <c r="G105" t="n">
-        <v>25.06000000000001</v>
+        <v>25.06</v>
       </c>
       <c r="H105" t="n">
         <v>-91.95000000000002</v>
@@ -5596,7 +5596,7 @@
         <v>-266.61</v>
       </c>
       <c r="H110" t="n">
-        <v>-460.6999999999999</v>
+        <v>-460.7</v>
       </c>
       <c r="I110" t="n">
         <v>-40.8</v>
@@ -5734,7 +5734,7 @@
         <v>-1004.29</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.6399999999999997</v>
+        <v>-0.6399999999999998</v>
       </c>
       <c r="H113" t="n">
         <v>-1004.93</v>
@@ -6442,7 +6442,7 @@
         <v>120.34</v>
       </c>
       <c r="H128" t="n">
-        <v>-91.76999999999998</v>
+        <v>-91.76999999999997</v>
       </c>
       <c r="I128" t="n">
         <v>-11.92</v>
@@ -6630,7 +6630,7 @@
         <v>-138.91</v>
       </c>
       <c r="H132" t="n">
-        <v>-358.5699999999999</v>
+        <v>-358.57</v>
       </c>
       <c r="I132" t="n">
         <v>-1.27</v>
@@ -6768,7 +6768,7 @@
         <v>-73.49000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>-58.76000000000001</v>
+        <v>-58.76</v>
       </c>
       <c r="H135" t="n">
         <v>-132.25</v>
@@ -6956,10 +6956,10 @@
         <v>-750.27</v>
       </c>
       <c r="G139" t="n">
-        <v>360.18</v>
+        <v>360.1800000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>-390.09</v>
+        <v>-390.0899999999999</v>
       </c>
       <c r="I139" t="n">
         <v>516.37</v>
@@ -7990,7 +7990,7 @@
         <v>76.37</v>
       </c>
       <c r="G161" t="n">
-        <v>-48.86</v>
+        <v>-48.85999999999999</v>
       </c>
       <c r="H161" t="n">
         <v>27.51000000000001</v>
@@ -8225,7 +8225,7 @@
         <v>402.65</v>
       </c>
       <c r="G166" t="n">
-        <v>550.3199999999999</v>
+        <v>550.3200000000001</v>
       </c>
       <c r="H166" t="n">
         <v>952.97</v>
@@ -9259,7 +9259,7 @@
         <v>507.97</v>
       </c>
       <c r="G188" t="n">
-        <v>564.03</v>
+        <v>564.0300000000001</v>
       </c>
       <c r="H188" t="n">
         <v>1072</v>
@@ -9638,7 +9638,7 @@
         <v>-195.41</v>
       </c>
       <c r="H196" t="n">
-        <v>45.24000000000001</v>
+        <v>45.23999999999998</v>
       </c>
       <c r="I196" t="n">
         <v>-78.16</v>
@@ -10105,10 +10105,10 @@
         <v>-231.81</v>
       </c>
       <c r="G206" t="n">
-        <v>-515.54</v>
+        <v>-515.5400000000001</v>
       </c>
       <c r="H206" t="n">
-        <v>-747.3499999999999</v>
+        <v>-747.3500000000001</v>
       </c>
       <c r="I206" t="n">
         <v>11.97</v>
@@ -10669,10 +10669,10 @@
         <v>-516.75</v>
       </c>
       <c r="G218" t="n">
-        <v>971.12</v>
+        <v>971.1200000000001</v>
       </c>
       <c r="H218" t="n">
-        <v>454.37</v>
+        <v>454.3700000000001</v>
       </c>
       <c r="I218" t="n">
         <v>-0.05</v>
@@ -10763,10 +10763,10 @@
         <v>-539.26</v>
       </c>
       <c r="G220" t="n">
-        <v>2092.619999999999</v>
+        <v>2092.62</v>
       </c>
       <c r="H220" t="n">
-        <v>1553.359999999999</v>
+        <v>1553.36</v>
       </c>
       <c r="I220" t="n">
         <v>-11.66</v>
@@ -10904,10 +10904,10 @@
         <v>175.97</v>
       </c>
       <c r="G223" t="n">
-        <v>-502.19</v>
+        <v>-502.1899999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>-326.22</v>
+        <v>-326.2199999999999</v>
       </c>
       <c r="I223" t="n">
         <v>73.44</v>
@@ -11186,10 +11186,10 @@
         <v>409.6999999999999</v>
       </c>
       <c r="G229" t="n">
-        <v>2696.6</v>
+        <v>2696.599999999999</v>
       </c>
       <c r="H229" t="n">
-        <v>3106.3</v>
+        <v>3106.299999999999</v>
       </c>
       <c r="I229" t="n">
         <v>25.29</v>
@@ -11280,7 +11280,7 @@
         <v>-290.47</v>
       </c>
       <c r="G231" t="n">
-        <v>-93.13000000000002</v>
+        <v>-93.13000000000005</v>
       </c>
       <c r="H231" t="n">
         <v>-383.6</v>
@@ -11327,7 +11327,7 @@
         <v>-241.42</v>
       </c>
       <c r="G232" t="n">
-        <v>-847.16</v>
+        <v>-847.1599999999999</v>
       </c>
       <c r="H232" t="n">
         <v>-1088.58</v>
@@ -11844,10 +11844,10 @@
         <v>-156.05</v>
       </c>
       <c r="G243" t="n">
-        <v>127.71</v>
+        <v>127.7100000000001</v>
       </c>
       <c r="H243" t="n">
-        <v>-28.33999999999995</v>
+        <v>-28.33999999999992</v>
       </c>
       <c r="I243" t="n">
         <v>207.84</v>
@@ -13301,10 +13301,10 @@
         <v>-342.12</v>
       </c>
       <c r="G274" t="n">
-        <v>867.7699999999999</v>
+        <v>867.77</v>
       </c>
       <c r="H274" t="n">
-        <v>525.6499999999999</v>
+        <v>525.65</v>
       </c>
       <c r="I274" t="n">
         <v>-11.85</v>
@@ -13348,7 +13348,7 @@
         <v>-213.34</v>
       </c>
       <c r="G275" t="n">
-        <v>87.61999999999999</v>
+        <v>87.61999999999998</v>
       </c>
       <c r="H275" t="n">
         <v>-125.72</v>
@@ -13395,7 +13395,7 @@
         <v>-60.03999999999994</v>
       </c>
       <c r="G276" t="n">
-        <v>327.03</v>
+        <v>327.0300000000001</v>
       </c>
       <c r="H276" t="n">
         <v>266.9900000000001</v>
@@ -13536,7 +13536,7 @@
         <v>445.8799999999999</v>
       </c>
       <c r="G279" t="n">
-        <v>864.9699999999999</v>
+        <v>864.97</v>
       </c>
       <c r="H279" t="n">
         <v>1310.85</v>
@@ -13677,10 +13677,10 @@
         <v>66</v>
       </c>
       <c r="G282" t="n">
-        <v>823.1499999999999</v>
+        <v>823.1500000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>889.1499999999999</v>
+        <v>889.1500000000001</v>
       </c>
       <c r="I282" t="n">
         <v>-49.98</v>
@@ -13806,10 +13806,10 @@
         <v>322.18</v>
       </c>
       <c r="C285" t="n">
-        <v>1314.13</v>
+        <v>1040.37</v>
       </c>
       <c r="D285" t="n">
-        <v>1108.63</v>
+        <v>1379.88</v>
       </c>
       <c r="E285" t="n">
         <v>12.25</v>
@@ -13818,13 +13818,13 @@
         <v>1308.67</v>
       </c>
       <c r="G285" t="n">
-        <v>2757.190000000001</v>
+        <v>2754.68</v>
       </c>
       <c r="H285" t="n">
-        <v>4065.860000000001</v>
+        <v>4063.35</v>
       </c>
       <c r="I285" t="n">
-        <v>-44.07</v>
+        <v>227.18</v>
       </c>
       <c r="J285" t="n">
         <v>1152.7</v>
@@ -13853,10 +13853,10 @@
         <v>409.96</v>
       </c>
       <c r="C286" t="n">
-        <v>-991.4400000000001</v>
+        <v>-991.92</v>
       </c>
       <c r="D286" t="n">
-        <v>-867.36</v>
+        <v>-897.6899999999999</v>
       </c>
       <c r="E286" t="n">
         <v>-93.90000000000001</v>
@@ -13865,13 +13865,13 @@
         <v>-1035.88</v>
       </c>
       <c r="G286" t="n">
-        <v>-1542.74</v>
+        <v>-1573.55</v>
       </c>
       <c r="H286" t="n">
-        <v>-2578.62</v>
+        <v>-2609.43</v>
       </c>
       <c r="I286" t="n">
-        <v>49.9</v>
+        <v>19.57</v>
       </c>
       <c r="J286" t="n">
         <v>-917.26</v>
@@ -13900,10 +13900,10 @@
         <v>65.26000000000001</v>
       </c>
       <c r="C287" t="n">
-        <v>-212.78</v>
+        <v>-252.85</v>
       </c>
       <c r="D287" t="n">
-        <v>-38.41</v>
+        <v>32.49000000000001</v>
       </c>
       <c r="E287" t="n">
         <v>454.49</v>
@@ -13912,13 +13912,13 @@
         <v>-2.970000000000001</v>
       </c>
       <c r="G287" t="n">
-        <v>268.5600000000001</v>
+        <v>299.39</v>
       </c>
       <c r="H287" t="n">
-        <v>265.59</v>
+        <v>296.42</v>
       </c>
       <c r="I287" t="n">
-        <v>114.22</v>
+        <v>185.12</v>
       </c>
       <c r="J287" t="n">
         <v>-152.63</v>
@@ -14617,7 +14617,7 @@
         <v>398.14</v>
       </c>
       <c r="G302" t="n">
-        <v>967.7099999999999</v>
+        <v>967.71</v>
       </c>
       <c r="H302" t="n">
         <v>1365.85</v>
@@ -14664,10 +14664,10 @@
         <v>-120.15</v>
       </c>
       <c r="G303" t="n">
-        <v>823.6300000000001</v>
+        <v>823.63</v>
       </c>
       <c r="H303" t="n">
-        <v>703.4800000000001</v>
+        <v>703.48</v>
       </c>
       <c r="I303" t="n">
         <v>-74.84999999999999</v>
@@ -14746,10 +14746,10 @@
         <v>11.45</v>
       </c>
       <c r="C305" t="n">
-        <v>220.96</v>
+        <v>571.98</v>
       </c>
       <c r="D305" t="n">
-        <v>1064.66</v>
+        <v>716.4400000000001</v>
       </c>
       <c r="E305" t="n">
         <v>441.07</v>
@@ -14758,13 +14758,13 @@
         <v>2653.74</v>
       </c>
       <c r="G305" t="n">
-        <v>1738.14</v>
+        <v>1740.94</v>
       </c>
       <c r="H305" t="n">
-        <v>4391.88</v>
+        <v>4394.68</v>
       </c>
       <c r="I305" t="n">
-        <v>300.91</v>
+        <v>-47.31</v>
       </c>
       <c r="J305" t="n">
         <v>763.75</v>
@@ -14852,10 +14852,10 @@
         <v>-108.28</v>
       </c>
       <c r="G307" t="n">
-        <v>10.87999999999997</v>
+        <v>10.88</v>
       </c>
       <c r="H307" t="n">
-        <v>-97.40000000000003</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="I307" t="n">
         <v>-19.51</v>
@@ -14993,10 +14993,10 @@
         <v>-188.64</v>
       </c>
       <c r="G310" t="n">
-        <v>969.8899999999999</v>
+        <v>969.89</v>
       </c>
       <c r="H310" t="n">
-        <v>781.2499999999999</v>
+        <v>781.25</v>
       </c>
       <c r="I310" t="n">
         <v>-4.54</v>
@@ -15181,10 +15181,10 @@
         <v>3.88000000000001</v>
       </c>
       <c r="G314" t="n">
-        <v>-462.75</v>
+        <v>-462.7499999999999</v>
       </c>
       <c r="H314" t="n">
-        <v>-458.87</v>
+        <v>-458.8699999999999</v>
       </c>
       <c r="I314" t="n">
         <v>-1.72</v>
@@ -15441,6 +15441,53 @@
       </c>
       <c r="O319" t="n">
         <v>12.91</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B320" t="n">
+        <v>-88.75</v>
+      </c>
+      <c r="C320" t="n">
+        <v>-44.36</v>
+      </c>
+      <c r="D320" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-20.72</v>
+      </c>
+      <c r="F320" t="n">
+        <v>-430.6899999999999</v>
+      </c>
+      <c r="G320" t="n">
+        <v>-118.11</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-548.8</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J320" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="n">
+        <v>-284.59</v>
+      </c>
+      <c r="M320" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="N320" t="n">
+        <v>-169.56</v>
+      </c>
+      <c r="O320" t="n">
+        <v>29.42</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,84 +433,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -639,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -799,7 +811,7 @@
         <v>-118.58</v>
       </c>
       <c r="G8" t="n">
-        <v>9.739999999999998</v>
+        <v>9.739999999999997</v>
       </c>
       <c r="H8" t="n">
         <v>-108.84</v>
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -968,7 +980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1081,7 +1093,7 @@
         <v>2025.54</v>
       </c>
       <c r="G14" t="n">
-        <v>60.99</v>
+        <v>60.98999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>2086.53</v>
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1156,7 +1168,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1203,7 +1215,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1250,7 +1262,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1297,7 +1309,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1344,7 +1356,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1438,7 +1450,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1579,7 +1591,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1732,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1814,7 +1826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2002,7 +2014,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2096,7 +2108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2331,7 +2343,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2378,7 +2390,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2397,10 +2409,10 @@
         <v>32.43</v>
       </c>
       <c r="G42" t="n">
-        <v>-24.97999999999999</v>
+        <v>-24.98</v>
       </c>
       <c r="H42" t="n">
-        <v>7.45000000000001</v>
+        <v>7.450000000000003</v>
       </c>
       <c r="I42" t="n">
         <v>-153.41</v>
@@ -2425,7 +2437,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2472,7 +2484,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2566,7 +2578,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2707,7 +2719,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2773,7 +2785,7 @@
         <v>-277.45</v>
       </c>
       <c r="G50" t="n">
-        <v>74.77000000000001</v>
+        <v>74.77</v>
       </c>
       <c r="H50" t="n">
         <v>-202.68</v>
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2848,7 +2860,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2895,7 +2907,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2942,7 +2954,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3130,7 +3142,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3149,7 +3161,7 @@
         <v>-793.46</v>
       </c>
       <c r="G58" t="n">
-        <v>-76.14</v>
+        <v>-76.14000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>-869.6</v>
@@ -3177,7 +3189,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3365,7 +3377,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3572,7 +3584,7 @@
         <v>-377.48</v>
       </c>
       <c r="G67" t="n">
-        <v>1.670000000000016</v>
+        <v>1.670000000000023</v>
       </c>
       <c r="H67" t="n">
         <v>-375.81</v>
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3622,7 +3634,7 @@
         <v>-332.61</v>
       </c>
       <c r="H68" t="n">
-        <v>-483.21</v>
+        <v>-483.2099999999999</v>
       </c>
       <c r="I68" t="n">
         <v>-168</v>
@@ -3647,7 +3659,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3694,7 +3706,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3741,7 +3753,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3929,7 +3941,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -3995,7 +4007,7 @@
         <v>-198.55</v>
       </c>
       <c r="G76" t="n">
-        <v>1.539999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="H76" t="n">
         <v>-197.01</v>
@@ -4023,7 +4035,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4164,7 +4176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4258,7 +4270,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4305,7 +4317,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4399,7 +4411,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4493,7 +4505,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4750,7 +4762,7 @@
         <v>288.92</v>
       </c>
       <c r="H92" t="n">
-        <v>49.99999999999994</v>
+        <v>50</v>
       </c>
       <c r="I92" t="n">
         <v>0.31</v>
@@ -4775,7 +4787,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4869,7 +4881,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5010,7 +5022,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5057,7 +5069,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5104,7 +5116,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5339,7 +5351,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5358,7 +5370,7 @@
         <v>-117.01</v>
       </c>
       <c r="G105" t="n">
-        <v>25.06</v>
+        <v>25.06000000000001</v>
       </c>
       <c r="H105" t="n">
         <v>-91.95000000000002</v>
@@ -5386,7 +5398,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5527,7 +5539,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5574,7 +5586,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5596,7 +5608,7 @@
         <v>-266.61</v>
       </c>
       <c r="H110" t="n">
-        <v>-460.7</v>
+        <v>-460.6999999999999</v>
       </c>
       <c r="I110" t="n">
         <v>-40.8</v>
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5734,7 +5746,7 @@
         <v>-1004.29</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.6399999999999998</v>
+        <v>-0.6399999999999997</v>
       </c>
       <c r="H113" t="n">
         <v>-1004.93</v>
@@ -5762,7 +5774,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5856,7 +5868,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5903,7 +5915,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6373,7 +6385,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6420,7 +6432,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6442,7 +6454,7 @@
         <v>120.34</v>
       </c>
       <c r="H128" t="n">
-        <v>-91.76999999999997</v>
+        <v>-91.76999999999998</v>
       </c>
       <c r="I128" t="n">
         <v>-11.92</v>
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6561,7 +6573,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6630,7 +6642,7 @@
         <v>-138.91</v>
       </c>
       <c r="H132" t="n">
-        <v>-358.57</v>
+        <v>-358.5699999999999</v>
       </c>
       <c r="I132" t="n">
         <v>-1.27</v>
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6749,7 +6761,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6768,7 +6780,7 @@
         <v>-73.49000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>-58.76</v>
+        <v>-58.76000000000001</v>
       </c>
       <c r="H135" t="n">
         <v>-132.25</v>
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6937,7 +6949,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6956,10 +6968,10 @@
         <v>-750.27</v>
       </c>
       <c r="G139" t="n">
-        <v>360.1800000000001</v>
+        <v>360.18</v>
       </c>
       <c r="H139" t="n">
-        <v>-390.0899999999999</v>
+        <v>-390.09</v>
       </c>
       <c r="I139" t="n">
         <v>516.37</v>
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7078,7 +7090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7172,7 +7184,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7219,7 +7231,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7266,7 +7278,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7313,7 +7325,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7360,7 +7372,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7407,7 +7419,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7454,7 +7466,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7501,7 +7513,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7595,7 +7607,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7642,7 +7654,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7736,7 +7748,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7783,7 +7795,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7830,7 +7842,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7877,7 +7889,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7924,7 +7936,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -7990,7 +8002,7 @@
         <v>76.37</v>
       </c>
       <c r="G161" t="n">
-        <v>-48.85999999999999</v>
+        <v>-48.86</v>
       </c>
       <c r="H161" t="n">
         <v>27.51000000000001</v>
@@ -8018,7 +8030,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8065,7 +8077,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8112,7 +8124,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8159,7 +8171,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8206,7 +8218,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8225,7 +8237,7 @@
         <v>402.65</v>
       </c>
       <c r="G166" t="n">
-        <v>550.3200000000001</v>
+        <v>550.3199999999999</v>
       </c>
       <c r="H166" t="n">
         <v>952.97</v>
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8347,7 +8359,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8441,7 +8453,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8488,7 +8500,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8535,7 +8547,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8582,7 +8594,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8629,7 +8641,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8676,7 +8688,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8723,7 +8735,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8817,7 +8829,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8864,7 +8876,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8911,7 +8923,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8958,7 +8970,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9005,7 +9017,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9146,7 +9158,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9193,7 +9205,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9240,7 +9252,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9259,7 +9271,7 @@
         <v>507.97</v>
       </c>
       <c r="G188" t="n">
-        <v>564.0300000000001</v>
+        <v>564.03</v>
       </c>
       <c r="H188" t="n">
         <v>1072</v>
@@ -9287,7 +9299,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9334,7 +9346,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9381,7 +9393,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9428,7 +9440,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9475,7 +9487,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9522,7 +9534,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9569,7 +9581,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9616,7 +9628,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9638,7 +9650,7 @@
         <v>-195.41</v>
       </c>
       <c r="H196" t="n">
-        <v>45.23999999999998</v>
+        <v>45.24000000000001</v>
       </c>
       <c r="I196" t="n">
         <v>-78.16</v>
@@ -9663,7 +9675,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9710,7 +9722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9757,7 +9769,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9851,7 +9863,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9898,7 +9910,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9945,7 +9957,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -9992,7 +10004,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10039,7 +10051,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10086,7 +10098,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10105,10 +10117,10 @@
         <v>-231.81</v>
       </c>
       <c r="G206" t="n">
-        <v>-515.5400000000001</v>
+        <v>-515.54</v>
       </c>
       <c r="H206" t="n">
-        <v>-747.3500000000001</v>
+        <v>-747.3499999999999</v>
       </c>
       <c r="I206" t="n">
         <v>11.97</v>
@@ -10133,7 +10145,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10180,7 +10192,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10227,7 +10239,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10274,7 +10286,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10368,7 +10380,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10462,7 +10474,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10509,7 +10521,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10556,7 +10568,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10603,7 +10615,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10669,10 +10681,10 @@
         <v>-516.75</v>
       </c>
       <c r="G218" t="n">
-        <v>971.1200000000001</v>
+        <v>971.12</v>
       </c>
       <c r="H218" t="n">
-        <v>454.3700000000001</v>
+        <v>454.37</v>
       </c>
       <c r="I218" t="n">
         <v>-0.05</v>
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10744,7 +10756,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10763,10 +10775,10 @@
         <v>-539.26</v>
       </c>
       <c r="G220" t="n">
-        <v>2092.62</v>
+        <v>2092.619999999999</v>
       </c>
       <c r="H220" t="n">
-        <v>1553.36</v>
+        <v>1553.359999999999</v>
       </c>
       <c r="I220" t="n">
         <v>-11.66</v>
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10838,7 +10850,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10885,7 +10897,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10904,10 +10916,10 @@
         <v>175.97</v>
       </c>
       <c r="G223" t="n">
-        <v>-502.1899999999999</v>
+        <v>-502.19</v>
       </c>
       <c r="H223" t="n">
-        <v>-326.2199999999999</v>
+        <v>-326.22</v>
       </c>
       <c r="I223" t="n">
         <v>73.44</v>
@@ -10932,7 +10944,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10979,7 +10991,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11026,7 +11038,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11120,7 +11132,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11167,7 +11179,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11186,10 +11198,10 @@
         <v>409.6999999999999</v>
       </c>
       <c r="G229" t="n">
-        <v>2696.599999999999</v>
+        <v>2696.6</v>
       </c>
       <c r="H229" t="n">
-        <v>3106.299999999999</v>
+        <v>3106.3</v>
       </c>
       <c r="I229" t="n">
         <v>25.29</v>
@@ -11214,7 +11226,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11261,7 +11273,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11280,7 +11292,7 @@
         <v>-290.47</v>
       </c>
       <c r="G231" t="n">
-        <v>-93.13000000000005</v>
+        <v>-93.13000000000002</v>
       </c>
       <c r="H231" t="n">
         <v>-383.6</v>
@@ -11308,7 +11320,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11327,7 +11339,7 @@
         <v>-241.42</v>
       </c>
       <c r="G232" t="n">
-        <v>-847.1599999999999</v>
+        <v>-847.16</v>
       </c>
       <c r="H232" t="n">
         <v>-1088.58</v>
@@ -11355,7 +11367,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11402,7 +11414,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11449,7 +11461,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11496,7 +11508,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11543,7 +11555,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11590,7 +11602,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11637,7 +11649,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11684,7 +11696,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11731,7 +11743,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11825,7 +11837,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11844,10 +11856,10 @@
         <v>-156.05</v>
       </c>
       <c r="G243" t="n">
-        <v>127.7100000000001</v>
+        <v>127.71</v>
       </c>
       <c r="H243" t="n">
-        <v>-28.33999999999992</v>
+        <v>-28.33999999999995</v>
       </c>
       <c r="I243" t="n">
         <v>207.84</v>
@@ -11872,7 +11884,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11919,7 +11931,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12013,7 +12025,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12060,7 +12072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12107,7 +12119,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12154,7 +12166,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12201,7 +12213,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12248,7 +12260,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12342,7 +12354,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12389,7 +12401,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12436,7 +12448,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12483,7 +12495,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12530,7 +12542,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12577,7 +12589,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12671,7 +12683,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12765,7 +12777,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12812,7 +12824,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12906,7 +12918,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12953,7 +12965,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13000,7 +13012,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13047,7 +13059,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13094,7 +13106,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13188,7 +13200,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13235,7 +13247,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13282,7 +13294,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13301,10 +13313,10 @@
         <v>-342.12</v>
       </c>
       <c r="G274" t="n">
-        <v>867.77</v>
+        <v>867.7699999999999</v>
       </c>
       <c r="H274" t="n">
-        <v>525.65</v>
+        <v>525.6499999999999</v>
       </c>
       <c r="I274" t="n">
         <v>-11.85</v>
@@ -13329,7 +13341,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13348,7 +13360,7 @@
         <v>-213.34</v>
       </c>
       <c r="G275" t="n">
-        <v>87.61999999999998</v>
+        <v>87.61999999999999</v>
       </c>
       <c r="H275" t="n">
         <v>-125.72</v>
@@ -13376,7 +13388,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13395,7 +13407,7 @@
         <v>-60.03999999999994</v>
       </c>
       <c r="G276" t="n">
-        <v>327.0300000000001</v>
+        <v>327.03</v>
       </c>
       <c r="H276" t="n">
         <v>266.9900000000001</v>
@@ -13423,7 +13435,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13470,7 +13482,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13517,7 +13529,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13536,7 +13548,7 @@
         <v>445.8799999999999</v>
       </c>
       <c r="G279" t="n">
-        <v>864.97</v>
+        <v>864.9699999999999</v>
       </c>
       <c r="H279" t="n">
         <v>1310.85</v>
@@ -13564,7 +13576,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13611,7 +13623,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13658,7 +13670,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13677,10 +13689,10 @@
         <v>66</v>
       </c>
       <c r="G282" t="n">
-        <v>823.1500000000001</v>
+        <v>823.1499999999999</v>
       </c>
       <c r="H282" t="n">
-        <v>889.1500000000001</v>
+        <v>889.1499999999999</v>
       </c>
       <c r="I282" t="n">
         <v>-49.98</v>
@@ -13705,7 +13717,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13752,7 +13764,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13799,7 +13811,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13846,7 +13858,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13893,7 +13905,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13940,7 +13952,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13987,7 +13999,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14034,7 +14046,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14081,7 +14093,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14128,7 +14140,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14175,7 +14187,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14222,7 +14234,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14269,7 +14281,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14316,7 +14328,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14363,7 +14375,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14410,7 +14422,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14457,7 +14469,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14617,7 +14629,7 @@
         <v>398.14</v>
       </c>
       <c r="G302" t="n">
-        <v>967.71</v>
+        <v>967.7099999999999</v>
       </c>
       <c r="H302" t="n">
         <v>1365.85</v>
@@ -14645,7 +14657,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14664,10 +14676,10 @@
         <v>-120.15</v>
       </c>
       <c r="G303" t="n">
-        <v>823.63</v>
+        <v>823.6300000000001</v>
       </c>
       <c r="H303" t="n">
-        <v>703.48</v>
+        <v>703.4800000000001</v>
       </c>
       <c r="I303" t="n">
         <v>-74.84999999999999</v>
@@ -14692,7 +14704,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14739,7 +14751,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14786,7 +14798,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14833,7 +14845,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14852,10 +14864,10 @@
         <v>-108.28</v>
       </c>
       <c r="G307" t="n">
-        <v>10.88</v>
+        <v>10.87999999999997</v>
       </c>
       <c r="H307" t="n">
-        <v>-97.40000000000001</v>
+        <v>-97.40000000000003</v>
       </c>
       <c r="I307" t="n">
         <v>-19.51</v>
@@ -14880,7 +14892,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14927,7 +14939,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -14993,10 +15005,10 @@
         <v>-188.64</v>
       </c>
       <c r="G310" t="n">
-        <v>969.89</v>
+        <v>969.8899999999999</v>
       </c>
       <c r="H310" t="n">
-        <v>781.25</v>
+        <v>781.2499999999999</v>
       </c>
       <c r="I310" t="n">
         <v>-4.54</v>
@@ -15021,7 +15033,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15068,7 +15080,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15115,7 +15127,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15162,7 +15174,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15181,10 +15193,10 @@
         <v>3.88000000000001</v>
       </c>
       <c r="G314" t="n">
-        <v>-462.7499999999999</v>
+        <v>-462.75</v>
       </c>
       <c r="H314" t="n">
-        <v>-458.8699999999999</v>
+        <v>-458.87</v>
       </c>
       <c r="I314" t="n">
         <v>-1.72</v>
@@ -15209,7 +15221,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15256,7 +15268,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15303,7 +15315,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">
@@ -15350,7 +15362,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>46297</v>
       </c>
       <c r="B318" t="n">
@@ -15397,7 +15409,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>46304</v>
       </c>
       <c r="B319" t="n">
@@ -15444,7 +15456,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>46311</v>
       </c>
       <c r="B320" t="n">

--- a/tcmb haftalık stok/output/hareket.xlsx
+++ b/tcmb haftalık stok/output/hareket.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,84 +421,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hisse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dibs_kesin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dibs_dolayli</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eurobond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>menkul_toplam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>toplam</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dibs_tersrepo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dibs_teminat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>dibs_odunc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>euro_genel_yonetim</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>euro_finansal_olmayan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>euro_banka</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>euro_diger_finansal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B2" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B4" t="n">
@@ -651,7 +639,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B5" t="n">
@@ -698,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B6" t="n">
@@ -745,7 +733,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B7" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B8" t="n">
@@ -811,7 +799,7 @@
         <v>-118.58</v>
       </c>
       <c r="G8" t="n">
-        <v>9.739999999999997</v>
+        <v>9.739999999999998</v>
       </c>
       <c r="H8" t="n">
         <v>-108.84</v>
@@ -839,7 +827,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B10" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B11" t="n">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B12" t="n">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B13" t="n">
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B14" t="n">
@@ -1093,7 +1081,7 @@
         <v>2025.54</v>
       </c>
       <c r="G14" t="n">
-        <v>60.98999999999999</v>
+        <v>60.99</v>
       </c>
       <c r="H14" t="n">
         <v>2086.53</v>
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B15" t="n">
@@ -1168,7 +1156,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B16" t="n">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B17" t="n">
@@ -1262,7 +1250,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -1309,7 +1297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B19" t="n">
@@ -1356,7 +1344,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1391,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B21" t="n">
@@ -1450,7 +1438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B22" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B23" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B24" t="n">
@@ -1591,7 +1579,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B25" t="n">
@@ -1638,7 +1626,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B26" t="n">
@@ -1685,7 +1673,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B27" t="n">
@@ -1732,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B28" t="n">
@@ -1779,7 +1767,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B29" t="n">
@@ -1826,7 +1814,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B30" t="n">
@@ -1873,7 +1861,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B31" t="n">
@@ -1920,7 +1908,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B32" t="n">
@@ -1967,7 +1955,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B33" t="n">
@@ -2014,7 +2002,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B34" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B35" t="n">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B36" t="n">
@@ -2155,7 +2143,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B37" t="n">
@@ -2202,7 +2190,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B38" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B39" t="n">
@@ -2296,7 +2284,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B40" t="n">
@@ -2343,7 +2331,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B41" t="n">
@@ -2390,7 +2378,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B42" t="n">
@@ -2409,10 +2397,10 @@
         <v>32.43</v>
       </c>
       <c r="G42" t="n">
-        <v>-24.98</v>
+        <v>-24.97999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>7.450000000000003</v>
+        <v>7.45000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>-153.41</v>
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B43" t="n">
@@ -2484,7 +2472,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B44" t="n">
@@ -2531,7 +2519,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B45" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B46" t="n">
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B47" t="n">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B48" t="n">
@@ -2719,7 +2707,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B49" t="n">
@@ -2766,7 +2754,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B50" t="n">
@@ -2785,7 +2773,7 @@
         <v>-277.45</v>
       </c>
       <c r="G50" t="n">
-        <v>74.77</v>
+        <v>74.77000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>-202.68</v>
@@ -2813,7 +2801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B51" t="n">
@@ -2860,7 +2848,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B52" t="n">
@@ -2907,7 +2895,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B53" t="n">
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B54" t="n">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B55" t="n">
@@ -3048,7 +3036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B56" t="n">
@@ -3095,7 +3083,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B57" t="n">
@@ -3142,7 +3130,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B58" t="n">
@@ -3161,7 +3149,7 @@
         <v>-793.46</v>
       </c>
       <c r="G58" t="n">
-        <v>-76.14000000000001</v>
+        <v>-76.14</v>
       </c>
       <c r="H58" t="n">
         <v>-869.6</v>
@@ -3189,7 +3177,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B59" t="n">
@@ -3236,7 +3224,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B60" t="n">
@@ -3283,7 +3271,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B61" t="n">
@@ -3330,7 +3318,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B62" t="n">
@@ -3377,7 +3365,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B63" t="n">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B64" t="n">
@@ -3471,7 +3459,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B65" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B66" t="n">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B67" t="n">
@@ -3584,7 +3572,7 @@
         <v>-377.48</v>
       </c>
       <c r="G67" t="n">
-        <v>1.670000000000023</v>
+        <v>1.670000000000016</v>
       </c>
       <c r="H67" t="n">
         <v>-375.81</v>
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B68" t="n">
@@ -3634,7 +3622,7 @@
         <v>-332.61</v>
       </c>
       <c r="H68" t="n">
-        <v>-483.2099999999999</v>
+        <v>-483.21</v>
       </c>
       <c r="I68" t="n">
         <v>-168</v>
@@ -3659,7 +3647,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B69" t="n">
@@ -3706,7 +3694,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B70" t="n">
@@ -3753,7 +3741,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B71" t="n">
@@ -3800,7 +3788,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B72" t="n">
@@ -3847,7 +3835,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B73" t="n">
@@ -3894,7 +3882,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B74" t="n">
@@ -3941,7 +3929,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B75" t="n">
@@ -3988,7 +3976,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B76" t="n">
@@ -4007,7 +3995,7 @@
         <v>-198.55</v>
       </c>
       <c r="G76" t="n">
-        <v>1.54</v>
+        <v>1.539999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>-197.01</v>
@@ -4035,7 +4023,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B77" t="n">
@@ -4082,7 +4070,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B78" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B79" t="n">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B80" t="n">
@@ -4223,7 +4211,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B81" t="n">
@@ -4270,7 +4258,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B82" t="n">
@@ -4317,7 +4305,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B83" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B84" t="n">
@@ -4411,7 +4399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B85" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B86" t="n">
@@ -4505,7 +4493,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B87" t="n">
@@ -4552,7 +4540,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B88" t="n">
@@ -4599,7 +4587,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B89" t="n">
@@ -4646,7 +4634,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B90" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B91" t="n">
@@ -4740,7 +4728,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B92" t="n">
@@ -4762,7 +4750,7 @@
         <v>288.92</v>
       </c>
       <c r="H92" t="n">
-        <v>50</v>
+        <v>49.99999999999994</v>
       </c>
       <c r="I92" t="n">
         <v>0.31</v>
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B93" t="n">
@@ -4834,7 +4822,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B94" t="n">
@@ -4881,7 +4869,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B95" t="n">
@@ -4928,7 +4916,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B96" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B97" t="n">
@@ -5022,7 +5010,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B98" t="n">
@@ -5069,7 +5057,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B99" t="n">
@@ -5116,7 +5104,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B100" t="n">
@@ -5163,7 +5151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B101" t="n">
@@ -5210,7 +5198,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B102" t="n">
@@ -5257,7 +5245,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B103" t="n">
@@ -5304,7 +5292,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B104" t="n">
@@ -5351,7 +5339,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B105" t="n">
@@ -5370,7 +5358,7 @@
         <v>-117.01</v>
       </c>
       <c r="G105" t="n">
-        <v>25.06000000000001</v>
+        <v>25.06</v>
       </c>
       <c r="H105" t="n">
         <v>-91.95000000000002</v>
@@ -5398,7 +5386,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B106" t="n">
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B107" t="n">
@@ -5492,7 +5480,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B108" t="n">
@@ -5539,7 +5527,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B109" t="n">
@@ -5586,7 +5574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B110" t="n">
@@ -5608,7 +5596,7 @@
         <v>-266.61</v>
       </c>
       <c r="H110" t="n">
-        <v>-460.6999999999999</v>
+        <v>-460.7</v>
       </c>
       <c r="I110" t="n">
         <v>-40.8</v>
@@ -5633,7 +5621,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B111" t="n">
@@ -5680,7 +5668,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B112" t="n">
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B113" t="n">
@@ -5746,7 +5734,7 @@
         <v>-1004.29</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.6399999999999997</v>
+        <v>-0.6399999999999998</v>
       </c>
       <c r="H113" t="n">
         <v>-1004.93</v>
@@ -5774,7 +5762,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B114" t="n">
@@ -5821,7 +5809,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B115" t="n">
@@ -5868,7 +5856,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B116" t="n">
@@ -5915,7 +5903,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B117" t="n">
@@ -5962,7 +5950,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B118" t="n">
@@ -6009,7 +5997,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B119" t="n">
@@ -6056,7 +6044,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B120" t="n">
@@ -6103,7 +6091,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B121" t="n">
@@ -6150,7 +6138,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B122" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B123" t="n">
@@ -6244,7 +6232,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B124" t="n">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B125" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B126" t="n">
@@ -6385,7 +6373,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B127" t="n">
@@ -6432,7 +6420,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B128" t="n">
@@ -6454,7 +6442,7 @@
         <v>120.34</v>
       </c>
       <c r="H128" t="n">
-        <v>-91.76999999999998</v>
+        <v>-91.76999999999997</v>
       </c>
       <c r="I128" t="n">
         <v>-11.92</v>
@@ -6479,7 +6467,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B129" t="n">
@@ -6526,7 +6514,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B130" t="n">
@@ -6573,7 +6561,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B131" t="n">
@@ -6620,7 +6608,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B132" t="n">
@@ -6642,7 +6630,7 @@
         <v>-138.91</v>
       </c>
       <c r="H132" t="n">
-        <v>-358.5699999999999</v>
+        <v>-358.57</v>
       </c>
       <c r="I132" t="n">
         <v>-1.27</v>
@@ -6667,7 +6655,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B133" t="n">
@@ -6714,7 +6702,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B134" t="n">
@@ -6761,7 +6749,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B135" t="n">
@@ -6780,7 +6768,7 @@
         <v>-73.49000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>-58.76000000000001</v>
+        <v>-58.76</v>
       </c>
       <c r="H135" t="n">
         <v>-132.25</v>
@@ -6808,7 +6796,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B136" t="n">
@@ -6855,7 +6843,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B137" t="n">
@@ -6902,7 +6890,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B138" t="n">
@@ -6949,7 +6937,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B139" t="n">
@@ -6968,10 +6956,10 @@
         <v>-750.27</v>
       </c>
       <c r="G139" t="n">
-        <v>360.18</v>
+        <v>360.1800000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>-390.09</v>
+        <v>-390.0899999999999</v>
       </c>
       <c r="I139" t="n">
         <v>516.37</v>
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B140" t="n">
@@ -7043,7 +7031,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B141" t="n">
@@ -7090,7 +7078,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B142" t="n">
@@ -7137,7 +7125,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B143" t="n">
@@ -7184,7 +7172,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B144" t="n">
@@ -7231,7 +7219,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B145" t="n">
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B146" t="n">
@@ -7325,7 +7313,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B147" t="n">
@@ -7372,7 +7360,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B148" t="n">
@@ -7419,7 +7407,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B149" t="n">
@@ -7466,7 +7454,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B150" t="n">
@@ -7513,7 +7501,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B151" t="n">
@@ -7560,7 +7548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B152" t="n">
@@ -7607,7 +7595,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B153" t="n">
@@ -7654,7 +7642,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B154" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B155" t="n">
@@ -7748,7 +7736,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B156" t="n">
@@ -7795,7 +7783,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B157" t="n">
@@ -7842,7 +7830,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B158" t="n">
@@ -7889,7 +7877,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B159" t="n">
@@ -7936,7 +7924,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B160" t="n">
@@ -7983,7 +7971,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B161" t="n">
@@ -8002,7 +7990,7 @@
         <v>76.37</v>
       </c>
       <c r="G161" t="n">
-        <v>-48.86</v>
+        <v>-48.85999999999999</v>
       </c>
       <c r="H161" t="n">
         <v>27.51000000000001</v>
@@ -8030,7 +8018,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B162" t="n">
@@ -8077,7 +8065,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B163" t="n">
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B164" t="n">
@@ -8171,7 +8159,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B165" t="n">
@@ -8218,7 +8206,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B166" t="n">
@@ -8237,7 +8225,7 @@
         <v>402.65</v>
       </c>
       <c r="G166" t="n">
-        <v>550.3199999999999</v>
+        <v>550.3200000000001</v>
       </c>
       <c r="H166" t="n">
         <v>952.97</v>
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B167" t="n">
@@ -8312,7 +8300,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B168" t="n">
@@ -8359,7 +8347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B169" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B170" t="n">
@@ -8453,7 +8441,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B171" t="n">
@@ -8500,7 +8488,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B172" t="n">
@@ -8547,7 +8535,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B173" t="n">
@@ -8594,7 +8582,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B174" t="n">
@@ -8641,7 +8629,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B175" t="n">
@@ -8688,7 +8676,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B176" t="n">
@@ -8735,7 +8723,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B177" t="n">
@@ -8782,7 +8770,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B178" t="n">
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B179" t="n">
@@ -8876,7 +8864,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B180" t="n">
@@ -8923,7 +8911,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B181" t="n">
@@ -8970,7 +8958,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B182" t="n">
@@ -9017,7 +9005,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B183" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B184" t="n">
@@ -9111,7 +9099,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B185" t="n">
@@ -9158,7 +9146,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B186" t="n">
@@ -9205,7 +9193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B187" t="n">
@@ -9252,7 +9240,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B188" t="n">
@@ -9271,7 +9259,7 @@
         <v>507.97</v>
       </c>
       <c r="G188" t="n">
-        <v>564.03</v>
+        <v>564.0300000000001</v>
       </c>
       <c r="H188" t="n">
         <v>1072</v>
@@ -9299,7 +9287,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B189" t="n">
@@ -9346,7 +9334,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B190" t="n">
@@ -9393,7 +9381,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B191" t="n">
@@ -9440,7 +9428,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B192" t="n">
@@ -9487,7 +9475,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B193" t="n">
@@ -9534,7 +9522,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B194" t="n">
@@ -9581,7 +9569,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B195" t="n">
@@ -9628,7 +9616,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -9650,7 +9638,7 @@
         <v>-195.41</v>
       </c>
       <c r="H196" t="n">
-        <v>45.24000000000001</v>
+        <v>45.23999999999998</v>
       </c>
       <c r="I196" t="n">
         <v>-78.16</v>
@@ -9675,7 +9663,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B197" t="n">
@@ -9722,7 +9710,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B198" t="n">
@@ -9769,7 +9757,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B199" t="n">
@@ -9816,7 +9804,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B200" t="n">
@@ -9863,7 +9851,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B201" t="n">
@@ -9910,7 +9898,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B202" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B203" t="n">
@@ -10004,7 +9992,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B204" t="n">
@@ -10051,7 +10039,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B205" t="n">
@@ -10098,7 +10086,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B206" t="n">
@@ -10117,10 +10105,10 @@
         <v>-231.81</v>
       </c>
       <c r="G206" t="n">
-        <v>-515.54</v>
+        <v>-515.5400000000001</v>
       </c>
       <c r="H206" t="n">
-        <v>-747.3499999999999</v>
+        <v>-747.3500000000001</v>
       </c>
       <c r="I206" t="n">
         <v>11.97</v>
@@ -10145,7 +10133,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B207" t="n">
@@ -10192,7 +10180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B208" t="n">
@@ -10239,7 +10227,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B209" t="n">
@@ -10286,7 +10274,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B210" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B211" t="n">
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B212" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B213" t="n">
@@ -10474,7 +10462,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B214" t="n">
@@ -10521,7 +10509,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B215" t="n">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B216" t="n">
@@ -10615,7 +10603,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B217" t="n">
@@ -10662,7 +10650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B218" t="n">
@@ -10681,10 +10669,10 @@
         <v>-516.75</v>
       </c>
       <c r="G218" t="n">
-        <v>971.12</v>
+        <v>971.1200000000001</v>
       </c>
       <c r="H218" t="n">
-        <v>454.37</v>
+        <v>454.3700000000001</v>
       </c>
       <c r="I218" t="n">
         <v>-0.05</v>
@@ -10709,7 +10697,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B219" t="n">
@@ -10756,7 +10744,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B220" t="n">
@@ -10775,10 +10763,10 @@
         <v>-539.26</v>
       </c>
       <c r="G220" t="n">
-        <v>2092.619999999999</v>
+        <v>2092.62</v>
       </c>
       <c r="H220" t="n">
-        <v>1553.359999999999</v>
+        <v>1553.36</v>
       </c>
       <c r="I220" t="n">
         <v>-11.66</v>
@@ -10803,7 +10791,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B221" t="n">
@@ -10850,7 +10838,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B222" t="n">
@@ -10897,7 +10885,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B223" t="n">
@@ -10916,10 +10904,10 @@
         <v>175.97</v>
       </c>
       <c r="G223" t="n">
-        <v>-502.19</v>
+        <v>-502.1899999999999</v>
       </c>
       <c r="H223" t="n">
-        <v>-326.22</v>
+        <v>-326.2199999999999</v>
       </c>
       <c r="I223" t="n">
         <v>73.44</v>
@@ -10944,7 +10932,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B224" t="n">
@@ -10991,7 +10979,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B225" t="n">
@@ -11038,7 +11026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B226" t="n">
@@ -11085,7 +11073,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B227" t="n">
@@ -11132,7 +11120,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B228" t="n">
@@ -11179,7 +11167,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B229" t="n">
@@ -11198,10 +11186,10 @@
         <v>409.6999999999999</v>
       </c>
       <c r="G229" t="n">
-        <v>2696.6</v>
+        <v>2696.599999999999</v>
       </c>
       <c r="H229" t="n">
-        <v>3106.3</v>
+        <v>3106.299999999999</v>
       </c>
       <c r="I229" t="n">
         <v>25.29</v>
@@ -11226,7 +11214,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B230" t="n">
@@ -11273,7 +11261,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B231" t="n">
@@ -11292,7 +11280,7 @@
         <v>-290.47</v>
       </c>
       <c r="G231" t="n">
-        <v>-93.13000000000002</v>
+        <v>-93.13000000000005</v>
       </c>
       <c r="H231" t="n">
         <v>-383.6</v>
@@ -11320,7 +11308,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B232" t="n">
@@ -11339,7 +11327,7 @@
         <v>-241.42</v>
       </c>
       <c r="G232" t="n">
-        <v>-847.16</v>
+        <v>-847.1599999999999</v>
       </c>
       <c r="H232" t="n">
         <v>-1088.58</v>
@@ -11367,7 +11355,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B233" t="n">
@@ -11414,7 +11402,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B234" t="n">
@@ -11461,7 +11449,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B235" t="n">
@@ -11508,7 +11496,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B236" t="n">
@@ -11555,7 +11543,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B237" t="n">
@@ -11602,7 +11590,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B238" t="n">
@@ -11649,7 +11637,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B239" t="n">
@@ -11696,7 +11684,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B240" t="n">
@@ -11743,7 +11731,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B241" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B242" t="n">
@@ -11837,7 +11825,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B243" t="n">
@@ -11856,10 +11844,10 @@
         <v>-156.05</v>
       </c>
       <c r="G243" t="n">
-        <v>127.71</v>
+        <v>127.7100000000001</v>
       </c>
       <c r="H243" t="n">
-        <v>-28.33999999999995</v>
+        <v>-28.33999999999992</v>
       </c>
       <c r="I243" t="n">
         <v>207.84</v>
@@ -11884,7 +11872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B244" t="n">
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B245" t="n">
@@ -11978,7 +11966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B246" t="n">
@@ -12025,7 +12013,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B247" t="n">
@@ -12072,7 +12060,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B248" t="n">
@@ -12119,7 +12107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B249" t="n">
@@ -12166,7 +12154,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B250" t="n">
@@ -12213,7 +12201,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B251" t="n">
@@ -12260,7 +12248,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B252" t="n">
@@ -12307,7 +12295,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B253" t="n">
@@ -12354,7 +12342,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B254" t="n">
@@ -12401,7 +12389,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B255" t="n">
@@ -12448,7 +12436,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B256" t="n">
@@ -12495,7 +12483,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B257" t="n">
@@ -12542,7 +12530,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B258" t="n">
@@ -12589,7 +12577,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B259" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B260" t="n">
@@ -12683,7 +12671,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B261" t="n">
@@ -12730,7 +12718,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B262" t="n">
@@ -12777,7 +12765,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B263" t="n">
@@ -12824,7 +12812,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B264" t="n">
@@ -12871,7 +12859,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B265" t="n">
@@ -12918,7 +12906,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B266" t="n">
@@ -12965,7 +12953,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B267" t="n">
@@ -13012,7 +13000,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B268" t="n">
@@ -13059,7 +13047,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B269" t="n">
@@ -13106,7 +13094,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B270" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B271" t="n">
@@ -13200,7 +13188,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B272" t="n">
@@ -13247,7 +13235,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B273" t="n">
@@ -13294,7 +13282,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B274" t="n">
@@ -13313,10 +13301,10 @@
         <v>-342.12</v>
       </c>
       <c r="G274" t="n">
-        <v>867.7699999999999</v>
+        <v>867.77</v>
       </c>
       <c r="H274" t="n">
-        <v>525.6499999999999</v>
+        <v>525.65</v>
       </c>
       <c r="I274" t="n">
         <v>-11.85</v>
@@ -13341,7 +13329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B275" t="n">
@@ -13360,7 +13348,7 @@
         <v>-213.34</v>
       </c>
       <c r="G275" t="n">
-        <v>87.61999999999999</v>
+        <v>87.61999999999998</v>
       </c>
       <c r="H275" t="n">
         <v>-125.72</v>
@@ -13388,7 +13376,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B276" t="n">
@@ -13407,7 +13395,7 @@
         <v>-60.03999999999994</v>
       </c>
       <c r="G276" t="n">
-        <v>327.03</v>
+        <v>327.0300000000001</v>
       </c>
       <c r="H276" t="n">
         <v>266.9900000000001</v>
@@ -13435,7 +13423,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B277" t="n">
@@ -13482,7 +13470,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B278" t="n">
@@ -13529,7 +13517,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B279" t="n">
@@ -13548,7 +13536,7 @@
         <v>445.8799999999999</v>
       </c>
       <c r="G279" t="n">
-        <v>864.9699999999999</v>
+        <v>864.97</v>
       </c>
       <c r="H279" t="n">
         <v>1310.85</v>
@@ -13576,7 +13564,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B280" t="n">
@@ -13623,7 +13611,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B281" t="n">
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B282" t="n">
@@ -13689,10 +13677,10 @@
         <v>66</v>
       </c>
       <c r="G282" t="n">
-        <v>823.1499999999999</v>
+        <v>823.1500000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>889.1499999999999</v>
+        <v>889.1500000000001</v>
       </c>
       <c r="I282" t="n">
         <v>-49.98</v>
@@ -13717,7 +13705,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B283" t="n">
@@ -13764,7 +13752,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B284" t="n">
@@ -13811,7 +13799,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B285" t="n">
@@ -13858,7 +13846,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B286" t="n">
@@ -13905,7 +13893,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B287" t="n">
@@ -13952,7 +13940,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B288" t="n">
@@ -13999,7 +13987,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B289" t="n">
@@ -14046,7 +14034,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B290" t="n">
@@ -14093,7 +14081,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B291" t="n">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B292" t="n">
@@ -14187,7 +14175,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B293" t="n">
@@ -14234,7 +14222,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B294" t="n">
@@ -14281,7 +14269,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B295" t="n">
@@ -14328,7 +14316,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B296" t="n">
@@ -14375,7 +14363,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B297" t="n">
@@ -14422,7 +14410,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B298" t="n">
@@ -14469,7 +14457,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B299" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B300" t="n">
@@ -14563,7 +14551,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B301" t="n">
@@ -14610,7 +14598,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B302" t="n">
@@ -14629,7 +14617,7 @@
         <v>398.14</v>
       </c>
       <c r="G302" t="n">
-        <v>967.7099999999999</v>
+        <v>967.71</v>
       </c>
       <c r="H302" t="n">
         <v>1365.85</v>
@@ -14657,7 +14645,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B303" t="n">
@@ -14676,10 +14664,10 @@
         <v>-120.15</v>
       </c>
       <c r="G303" t="n">
-        <v>823.6300000000001</v>
+        <v>823.63</v>
       </c>
       <c r="H303" t="n">
-        <v>703.4800000000001</v>
+        <v>703.48</v>
       </c>
       <c r="I303" t="n">
         <v>-74.84999999999999</v>
@@ -14704,7 +14692,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B304" t="n">
@@ -14751,7 +14739,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B305" t="n">
@@ -14798,7 +14786,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B306" t="n">
@@ -14845,7 +14833,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B307" t="n">
@@ -14864,10 +14852,10 @@
         <v>-108.28</v>
       </c>
       <c r="G307" t="n">
-        <v>10.87999999999997</v>
+        <v>10.88</v>
       </c>
       <c r="H307" t="n">
-        <v>-97.40000000000003</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="I307" t="n">
         <v>-19.51</v>
@@ -14892,7 +14880,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B308" t="n">
@@ -14939,7 +14927,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B309" t="n">
@@ -14986,7 +14974,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B310" t="n">
@@ -15005,10 +14993,10 @@
         <v>-188.64</v>
       </c>
       <c r="G310" t="n">
-        <v>969.8899999999999</v>
+        <v>969.89</v>
       </c>
       <c r="H310" t="n">
-        <v>781.2499999999999</v>
+        <v>781.25</v>
       </c>
       <c r="I310" t="n">
         <v>-4.54</v>
@@ -15033,7 +15021,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B311" t="n">
@@ -15080,7 +15068,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B312" t="n">
@@ -15127,7 +15115,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B313" t="n">
@@ -15174,7 +15162,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B314" t="n">
@@ -15193,10 +15181,10 @@
         <v>3.88000000000001</v>
       </c>
       <c r="G314" t="n">
-        <v>-462.75</v>
+        <v>-462.7499999999999</v>
       </c>
       <c r="H314" t="n">
-        <v>-458.87</v>
+        <v>-458.8699999999999</v>
       </c>
       <c r="I314" t="n">
         <v>-1.72</v>
@@ -15221,7 +15209,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B315" t="n">
@@ -15268,7 +15256,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B316" t="n">
@@ -15315,7 +15303,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B317" t="n">
@@ -15362,7 +15350,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B318" t="n">
@@ -15409,7 +15397,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="B319" t="n">
@@ -15456,7 +15444,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>46311</v>
       </c>
       <c r="B320" t="n">
